--- a/artfynd/A 18048-2021 artfynd.xlsx
+++ b/artfynd/A 18048-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2214,6 +2214,258 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>63181384</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högetorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579661</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6351878</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2011-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2011-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>63181385</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högetorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>578890</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6351836</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2011-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2011-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18048-2021 artfynd.xlsx
+++ b/artfynd/A 18048-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
